--- a/StructureDefinition-HivLabTestServiceRequest.xlsx
+++ b/StructureDefinition-HivLabTestServiceRequest.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-02T03:11:41+00:00</t>
+    <t>2025-03-13T17:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -794,7 +794,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred] and a valueset using LOINC Order codes is available [here](http://hl7.org/fhir/R4/valueset-diagnostic-requests.html).</t>
+    <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred].</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
@@ -1702,7 +1702,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="186.83203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-HivLabTestServiceRequest.xlsx
+++ b/StructureDefinition-HivLabTestServiceRequest.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T17:17:21+00:00</t>
+    <t>2025-03-13T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivLabTestServiceRequest.xlsx
+++ b/StructureDefinition-HivLabTestServiceRequest.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-13T17:18:21+00:00</t>
+    <t>2025-03-14T13:53:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
